--- a/demos/08_full_showcase/report.xlsx
+++ b/demos/08_full_showcase/report.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
@@ -593,6 +593,18 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Widget row (2D capture)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Widget</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
